--- a/agents/wansoft/test_data/ReporteVentasPorMesero2026-05-10.xlsx
+++ b/agents/wansoft/test_data/ReporteVentasPorMesero2026-05-10.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen de ventas por mesero" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ventas por mesero por grupo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Hoja4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ventas por mesero por grupo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen de ventas por mesero" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ventas por mesero por mesa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ventas por tipo de grupo" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,385 +416,927 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Reporte de Ventas por Mesero</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AMALAY Coffee &amp; Market</t>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sucursal: Café Amalay - Plaza Duendes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Periodo: 10/05/2026</t>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reporte del: 2026-05-10 al 2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Generado: 10/05/2026 22:30</t>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Reporte generado: 2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Total descuentos sobre cuentas:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reporte Ventas Por Mesero Por Grupo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Mesero</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tipo grupo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platillo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>IEPS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Personas atendidas</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Promedio por persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Brayan Berlanga Solis</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>14200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2272</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16472</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SIGNATURE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HALF  HALF COMBO</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1163</v>
+      </c>
+      <c r="J8" t="n">
+        <v>186</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SIGNATURE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HALF  HALF COMBO</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>232</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>270</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CHILAQUILES &amp; ENCHILADAS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CHILAQUILES</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>646</v>
+      </c>
+      <c r="J10" t="n">
+        <v>103</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>750</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CHILAQUILES &amp; ENCHILADAS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CHILAQUILES LIGHT</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>215</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>250</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CROISSANT NUTELLA</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>256</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>297</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CINAMMON ROLL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>99</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DESSERTS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NEW YORK CHEESECAKE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>224</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>260</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oscar Rios Alvarado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SIGNATURE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HALF  HALF COMBO</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>465</v>
+      </c>
+      <c r="J15" t="n">
+        <v>74</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>540</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Oscar Rios Alvarado</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CHOCOLATIN</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>118</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>138</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oscar Rios Alvarado</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ICE CREAM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NIEVE FRUTOS ROJOS</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>64</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Omar Aguilera</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CHILAQUILES &amp; ENCHILADAS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CHILAQUILES</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1508</v>
+      </c>
+      <c r="J18" t="n">
+        <v>241</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>1750</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Omar Aguilera</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CROISSANT NUTELLA</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>427</v>
+      </c>
+      <c r="J19" t="n">
+        <v>68</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>495</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Hector Enrique Rodriguez L.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SUNSHINE MUFFIN</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>167</v>
+      </c>
+      <c r="J20" t="n">
         <v>26</v>
       </c>
-      <c r="H7" t="n">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Oscar Rios Alvarado</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>12800</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2048</v>
-      </c>
-      <c r="E8" t="n">
-        <v>14848</v>
-      </c>
-      <c r="F8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>29</v>
-      </c>
-      <c r="H8" t="n">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Julio Cesar Hernández H.</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>11000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="E9" t="n">
-        <v>12760</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>26</v>
-      </c>
-      <c r="H9" t="n">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Omar Aguilera</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>13500</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E10" t="n">
-        <v>15660</v>
-      </c>
-      <c r="F10" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>35</v>
-      </c>
-      <c r="H10" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>194</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Hector Enrique Rodriguez L.</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>10200</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1632</v>
-      </c>
-      <c r="E11" t="n">
-        <v>11832</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>28</v>
-      </c>
-      <c r="H11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Daniela Edith Rico Segura</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1360</v>
-      </c>
-      <c r="E12" t="n">
-        <v>9860</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mauricio Rodriguez Rodriguez</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1248</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9048</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DESSERTS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DARK CHOCOLATE BROWNIE</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>336</v>
+      </c>
+      <c r="J21" t="n">
+        <v>53</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
         <v>390</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Alexis Alejandro Ocampo V.</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>816</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5916</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>16</v>
-      </c>
-      <c r="H14" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="M21" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>MESERO EVENTO</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>672</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4872</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" t="n">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CROISSANT NUTELLA</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>854</v>
+      </c>
+      <c r="J22" t="n">
+        <v>136</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>990</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MESERO EVENTO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DESSERTS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CARROT CAKE</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>465</v>
+      </c>
+      <c r="J23" t="n">
+        <v>74</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>540</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>APLICACIONES</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>3825</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>612</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4437</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>91125</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>14580</v>
-      </c>
-      <c r="E17" t="n">
-        <v>105705</v>
-      </c>
-      <c r="F17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G17" t="n">
-        <v>219</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SIGNATURE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HALF  HALF COMBO</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>697</v>
+      </c>
+      <c r="J24" t="n">
+        <v>111</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>810</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>APLICACIONES</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>POSTRES</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BAKERY</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CHOCOLATIN</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>118</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>138</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -808,24 +1350,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sucursal: Café Amalay - Plaza Duendes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reporte del: 2026-05-10 al 2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Reporte generado: 2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Total descuentos sobre cuentas:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reporte ventas por mesero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Mesero</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IEPS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Personas atendidas</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Promedio por persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brayan Berlanga Solis</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2272</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16472</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>26</v>
+      </c>
+      <c r="J8" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oscar Rios Alvarado</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12800</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2048</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14848</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Julio Cesar Hernández H.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12760</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Omar Aguilera</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13500</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15660</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hector Enrique Rodriguez L.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1632</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11832</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Daniela Edith Rico Segura</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9860</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mauricio Rodriguez Rodriguez</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9048</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Alexis Alejandro Ocampo V.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>816</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5916</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MESERO EVENTO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>672</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4872</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>APLICACIONES</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3825</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>612</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4437</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>91125</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14580</v>
+      </c>
+      <c r="G18" t="n">
+        <v>105705</v>
+      </c>
+      <c r="H18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>219</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
